--- a/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
@@ -750,14 +750,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45177.58487881858</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="21">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -803,26 +799,6 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="21">
       <c r="A32" s="24" t="inlineStr">
         <is>
@@ -854,7 +830,7 @@
       </c>
       <c r="C33" s="19" t="n"/>
       <c r="D33" s="13" t="n">
-        <v>88.527</v>
+        <v>94</v>
       </c>
       <c r="E33" s="14" t="n"/>
       <c r="F33" s="15" t="n"/>
@@ -872,7 +848,7 @@
       </c>
       <c r="C34" s="17" t="n"/>
       <c r="D34" s="13" t="n">
-        <v>70.05500000000001</v>
+        <v>75</v>
       </c>
       <c r="E34" s="14" t="n"/>
       <c r="F34" s="15" t="n"/>
@@ -890,7 +866,7 @@
       </c>
       <c r="C35" s="17" t="n"/>
       <c r="D35" s="13" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E35" s="14" t="n"/>
       <c r="F35" s="15" t="n"/>
@@ -908,7 +884,7 @@
       </c>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="13" t="n">
-        <v>150.921</v>
+        <v>161</v>
       </c>
       <c r="E36" s="14" t="n"/>
       <c r="F36" s="15" t="n"/>
@@ -926,7 +902,7 @@
       </c>
       <c r="C37" s="17" t="n"/>
       <c r="D37" s="13" t="n">
-        <v>108.349</v>
+        <v>115</v>
       </c>
       <c r="E37" s="14" t="n"/>
       <c r="F37" s="15" t="n"/>
@@ -944,7 +920,7 @@
       </c>
       <c r="C38" s="17" t="n"/>
       <c r="D38" s="13" t="n">
-        <v>95.05800000000001</v>
+        <v>101</v>
       </c>
       <c r="E38" s="14" t="n"/>
       <c r="F38" s="15" t="n"/>
@@ -952,7 +928,6 @@
     <row r="39">
       <c r="A39" s="8" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
@@ -960,7 +935,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -970,17 +944,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
@@ -944,17 +944,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
@@ -750,7 +750,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -944,17 +944,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
@@ -750,7 +750,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -944,17 +944,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
@@ -750,7 +750,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
@@ -750,7 +750,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA UNION DISMAY.xlsx
@@ -750,10 +750,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45266</v>
+        <v>45254.59211088095</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="21">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -799,6 +803,26 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="21">
       <c r="A32" s="24" t="inlineStr">
         <is>
@@ -830,7 +854,7 @@
       </c>
       <c r="C33" s="19" t="n"/>
       <c r="D33" s="13" t="n">
-        <v>94</v>
+        <v>120.97</v>
       </c>
       <c r="E33" s="14" t="n"/>
       <c r="F33" s="15" t="n"/>
@@ -848,7 +872,7 @@
       </c>
       <c r="C34" s="17" t="n"/>
       <c r="D34" s="13" t="n">
-        <v>75</v>
+        <v>96.52</v>
       </c>
       <c r="E34" s="14" t="n"/>
       <c r="F34" s="15" t="n"/>
@@ -866,7 +890,7 @@
       </c>
       <c r="C35" s="17" t="n"/>
       <c r="D35" s="13" t="n">
-        <v>70</v>
+        <v>90.09</v>
       </c>
       <c r="E35" s="14" t="n"/>
       <c r="F35" s="15" t="n"/>
@@ -884,7 +908,7 @@
       </c>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="13" t="n">
-        <v>161</v>
+        <v>207.2</v>
       </c>
       <c r="E36" s="14" t="n"/>
       <c r="F36" s="15" t="n"/>
@@ -902,7 +926,7 @@
       </c>
       <c r="C37" s="17" t="n"/>
       <c r="D37" s="13" t="n">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="E37" s="14" t="n"/>
       <c r="F37" s="15" t="n"/>
@@ -920,7 +944,7 @@
       </c>
       <c r="C38" s="17" t="n"/>
       <c r="D38" s="13" t="n">
-        <v>101</v>
+        <v>129.98</v>
       </c>
       <c r="E38" s="14" t="n"/>
       <c r="F38" s="15" t="n"/>
@@ -928,6 +952,7 @@
     <row r="39">
       <c r="A39" s="8" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
@@ -935,6 +960,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -944,17 +970,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
